--- a/src/assets/employees/rochdi.xlsx
+++ b/src/assets/employees/rochdi.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,13 +430,13 @@
         <v>additive clc_clsb</v>
       </c>
       <c r="D2" t="str">
-        <v>suivi bc additive</v>
+        <v>suivi bc additive (1-5) /09 / 2026</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F2" t="str">
-        <v>2026-09-07</v>
+        <v>2026-09-02</v>
       </c>
     </row>
     <row r="3">
@@ -450,13 +450,13 @@
         <v>sms2i</v>
       </c>
       <c r="D3" t="str">
-        <v>taches administrative</v>
+        <v>taches administrative ( camion et livraison )</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F3" t="str">
-        <v>2026-09-07</v>
+        <v>2026-09-01</v>
       </c>
     </row>
     <row r="4">
@@ -470,13 +470,13 @@
         <v>sms2i</v>
       </c>
       <c r="D4" t="str">
-        <v>dev cost projet</v>
+        <v>dev cost projet (codage )</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F4" t="str">
-        <v>2026-09-07</v>
+        <v>2026-09-01</v>
       </c>
     </row>
     <row r="5">
@@ -490,13 +490,13 @@
         <v>sonede</v>
       </c>
       <c r="D5" t="str">
-        <v>suivi bc sonede</v>
+        <v>suivi bc sonede ( 1-5) 09/2026</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="str">
-        <v>2026-09-07</v>
+        <v>2026-09-01</v>
       </c>
     </row>
     <row r="6">
@@ -507,21 +507,121 @@
         <v>it</v>
       </c>
       <c r="C6" t="str">
+        <v>sms2i</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Agilité drive + Trello + Daily metting  ( 2 h chaque jour )</v>
+      </c>
+      <c r="E6">
+        <v>48</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2026-09-01</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>rochdi</v>
+      </c>
+      <c r="B7" t="str">
+        <v>it</v>
+      </c>
+      <c r="C7" t="str">
         <v>additive clc_clsb</v>
       </c>
-      <c r="D6" t="str">
-        <v>Agilité</v>
-      </c>
-      <c r="E6">
-        <v>30</v>
-      </c>
-      <c r="F6" t="str">
+      <c r="D7" t="str">
+        <v>suivi bc additive (7-10) /09 / 2026</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+      <c r="F7" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>rochdi</v>
+      </c>
+      <c r="B8" t="str">
+        <v>it</v>
+      </c>
+      <c r="C8" t="str">
+        <v>sonede</v>
+      </c>
+      <c r="D8" t="str">
+        <v>suivi bc sonede ( 7-10) 09/2026</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8" t="str">
+        <v>2026-09-09</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>rochdi</v>
+      </c>
+      <c r="B9" t="str">
+        <v>it</v>
+      </c>
+      <c r="C9" t="str">
+        <v>sms2i</v>
+      </c>
+      <c r="D9" t="str">
+        <v>dev cost projet (codage )</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2026-09-04</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>rochdi</v>
+      </c>
+      <c r="B10" t="str">
+        <v>it</v>
+      </c>
+      <c r="C10" t="str">
+        <v>sms2i</v>
+      </c>
+      <c r="D10" t="str">
+        <v>dev cost projet (codage )</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10" t="str">
         <v>2026-09-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>rochdi</v>
+      </c>
+      <c r="B11" t="str">
+        <v>it</v>
+      </c>
+      <c r="C11" t="str">
+        <v>sms2i</v>
+      </c>
+      <c r="D11" t="str">
+        <v>dev cost projet (codage )</v>
+      </c>
+      <c r="E11">
+        <v>4</v>
+      </c>
+      <c r="F11" t="str">
+        <v>2026-09-08</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/src/assets/employees/rochdi.xlsx
+++ b/src/assets/employees/rochdi.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -619,9 +619,49 @@
         <v>2026-09-08</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>rochdi</v>
+      </c>
+      <c r="B12" t="str">
+        <v>it</v>
+      </c>
+      <c r="C12" t="str">
+        <v>sms2i</v>
+      </c>
+      <c r="D12" t="str">
+        <v>dev cost projet codage</v>
+      </c>
+      <c r="E12">
+        <v>4</v>
+      </c>
+      <c r="F12" t="str">
+        <v>2026-09-10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>rochdi</v>
+      </c>
+      <c r="B13" t="str">
+        <v>it</v>
+      </c>
+      <c r="C13" t="str">
+        <v>sms2i</v>
+      </c>
+      <c r="D13" t="str">
+        <v>dev cost projet (data)</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+      <c r="F13" t="str">
+        <v>2026-09-10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F13"/>
   </ignoredErrors>
 </worksheet>
 </file>